--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:07</t>
+    <t xml:space="preserve">2026-09-09 23:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:00</t>
+    <t xml:space="preserve">2026-09-17 13:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:58</t>
+    <t xml:space="preserve">2026-09-23 12:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:27</t>
+    <t xml:space="preserve">2026-10-02 13:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:23</t>
+    <t xml:space="preserve">2026-10-05 09:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -654,7 +654,7 @@
         <v>2018</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1759074.62</v>
+        <v>1759074.63</v>
       </c>
     </row>
     <row r="4">
@@ -739,7 +739,7 @@
         <v>2018</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1133640.12</v>
+        <v>1133640.13</v>
       </c>
     </row>
     <row r="9">
@@ -960,7 +960,7 @@
         <v>2018</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>796566.12</v>
+        <v>796566.13</v>
       </c>
     </row>
     <row r="22">
@@ -1062,7 +1062,7 @@
         <v>2018</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>781286.12</v>
+        <v>781286.13</v>
       </c>
     </row>
     <row r="28">
@@ -1147,7 +1147,7 @@
         <v>2018</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>711667.62</v>
+        <v>711667.63</v>
       </c>
     </row>
     <row r="33">
@@ -1419,7 +1419,7 @@
         <v>2018</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>626362.12</v>
+        <v>626362.13</v>
       </c>
     </row>
     <row r="49">
@@ -1504,7 +1504,7 @@
         <v>2018</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>557939.12</v>
+        <v>557939.13</v>
       </c>
     </row>
   </sheetData>
